--- a/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-labresult.xlsx
+++ b/jpcore-r4/feature/wg2-pathology/StructureDefinition-jp-observation-labresult.xlsx
@@ -758,7 +758,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministration_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationDispenseBase|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement|http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationStatement_Injection|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Procedure|http://jpfhir.jp/fhir/core/StructureDefinition/JP_Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -1990,7 +1990,7 @@
     <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](observation.html#notes) below.</t>
   </si>
   <si>
-    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではないん）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
+    <t>コンポーネントobservation は プライマリobservation としてのobservation リソースの中で同じ属性を共有し、常に単一のobservation の一部として扱われる（つまりそれらは分離可能ではない）。ただし、プライマリobservationのreference rangeはコンポーネント値に継承されないため、reference rangeは各コンポーネントobservation に適切であれば必要である。</t>
   </si>
   <si>
     <t>containment by OBX-4?</t>
